--- a/output/pdf_financials_xlsx/NURS.xlsx
+++ b/output/pdf_financials_xlsx/NURS.xlsx
@@ -3030,25 +3030,25 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.002061</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.02086</v>
       </c>
       <c r="D92" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.006826</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.451535</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.4681</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.694767</v>
       </c>
     </row>
     <row r="93">
@@ -5302,7 +5302,11 @@
           <t>Reserves 12</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
@@ -6389,7 +6393,11 @@
           <t>Reserves 10</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
@@ -7456,7 +7464,11 @@
           <t>Reserves 3,12</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>-</t>
@@ -8137,7 +8149,11 @@
           <t>Shared-based payment reserve 3,11</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>-</t>
@@ -8716,7 +8732,11 @@
           <t>Reserves (note 4)</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E87" s="5" t="n">
         <v>0.002061</v>
       </c>
@@ -20952,10 +20972,10 @@
         </is>
       </c>
       <c r="E327" s="5" t="n">
-        <v>0.072378</v>
+        <v>-0.072378</v>
       </c>
       <c r="F327" s="5" t="n">
-        <v>0.09468799999999999</v>
+        <v>-0.09468799999999999</v>
       </c>
       <c r="G327" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/NURS.xlsx
+++ b/output/pdf_financials_xlsx/NURS.xlsx
@@ -741,10 +741,10 @@
         <v>0</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.021102</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.016238</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0</v>
@@ -1199,10 +1199,10 @@
         <v>-5.99522</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-1.937351</v>
+        <v>-1.958453</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.405169</v>
+        <v>-0.421407</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>1.113967</v>
@@ -1255,10 +1255,10 @@
         <v>-5.957937</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.828962</v>
+        <v>-1.850064</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.224033</v>
+        <v>-0.240271</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>1.566739</v>
@@ -1287,10 +1287,10 @@
         <v>-139.5814293355099</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-15.89089565694275</v>
+        <v>-16.07423991458879</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-1.396303929592771</v>
+        <v>-1.497508587874039</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>4.427687770181284</v>
@@ -1370,25 +1370,25 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.010563</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.149843</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.006381</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>2.432421</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>1.783787</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>1.186942</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>15.649232</v>
       </c>
     </row>
     <row r="35">
@@ -1426,25 +1426,25 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.010563</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.149843</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.006381</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>2.432421</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>1.783787</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>1.186942</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>15.649232</v>
       </c>
     </row>
     <row r="37">
@@ -1762,25 +1762,25 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.016833</v>
+        <v>0.00627</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.156113</v>
+        <v>0.00627</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.046347</v>
+        <v>0.039966</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>2.503755</v>
+        <v>0.07133399999999999</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.936935</v>
+        <v>0.153148</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1.503079</v>
+        <v>0.316137</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>19.223497</v>
+        <v>3.574265</v>
       </c>
     </row>
     <row r="49">
@@ -3920,10 +3920,10 @@
         <v>0</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>0</v>
+        <v>-0.022217</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>0</v>
+        <v>-0.019174</v>
       </c>
       <c r="G124" s="3" t="n">
         <v>0</v>
@@ -3948,10 +3948,10 @@
         <v>0</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>0</v>
+        <v>-0.022217</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>0</v>
+        <v>-0.019174</v>
       </c>
       <c r="G125" s="3" t="n">
         <v>0</v>
@@ -4400,7 +4400,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E79" s="5" t="n">
@@ -11472,7 +11472,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr"/>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E141" t="inlineStr">
         <is>
           <t>-</t>
@@ -16935,7 +16939,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -18575,7 +18579,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">

--- a/output/pdf_financials_xlsx/NURS.xlsx
+++ b/output/pdf_financials_xlsx/NURS.xlsx
@@ -9850,7 +9850,11 @@
           <t>Additions to intangible asset</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
           <t>-</t>
@@ -12035,7 +12039,11 @@
           <t>Additions to intangible assets</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr"/>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E152" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/NURS.xlsx
+++ b/output/pdf_financials_xlsx/NURS.xlsx
@@ -2320,13 +2320,13 @@
         <v>0</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.121017</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.306808</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.317456</v>
       </c>
     </row>
     <row r="68">
@@ -3264,7 +3264,7 @@
         <v>0</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.004529</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>0</v>
@@ -3472,10 +3472,10 @@
         <v>0</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>0</v>
+        <v>0.09886</v>
       </c>
       <c r="H108" s="3" t="n">
-        <v>0</v>
+        <v>0.054814</v>
       </c>
     </row>
     <row r="109">
@@ -9252,7 +9252,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
           <t>-</t>
@@ -9303,7 +9307,11 @@
           <t>Impairment charge</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>AssetImpairmentCharge</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
           <t>-</t>
@@ -13428,7 +13436,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr"/>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E179" t="inlineStr">
         <is>
           <t>-</t>
